--- a/lab-standards/PKSF-lab-standard.xlsx
+++ b/lab-standards/PKSF-lab-standard.xlsx
@@ -19,6 +19,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graphic Design" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IT Freelancing" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobile Phone Servicing" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Housekeeping" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -110,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
@@ -143,6 +144,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -653,7 +666,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="16" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -677,7 +690,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -701,7 +714,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="16" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -725,7 +738,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="16" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -749,7 +762,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -773,7 +786,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="16" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -797,7 +810,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -821,7 +834,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="16" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -845,7 +858,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="14" t="n">
+      <c r="A24" s="16" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -869,7 +882,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="14" t="n">
+      <c r="A25" s="16" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -893,7 +906,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="14" t="n">
+      <c r="A26" s="16" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -917,7 +930,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="14" t="n">
+      <c r="A27" s="16" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -941,7 +954,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="14" t="n">
+      <c r="A28" s="16" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -965,7 +978,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="14" t="n">
+      <c r="A29" s="16" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -989,7 +1002,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="14" t="n">
+      <c r="A30" s="16" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -1013,7 +1026,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="14" t="n">
+      <c r="A31" s="16" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -1037,7 +1050,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="14" t="n">
+      <c r="A32" s="16" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -1061,7 +1074,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="14" t="n">
+      <c r="A33" s="16" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -1085,7 +1098,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="14" t="n">
+      <c r="A34" s="16" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -1109,7 +1122,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35" ht="14.15" customHeight="1">
-      <c r="A35" s="14" t="n">
+      <c r="A35" s="16" t="n">
         <v>20</v>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -1133,7 +1146,7 @@
       <c r="G35" s="9" t="n"/>
     </row>
     <row r="36" ht="14.15" customHeight="1">
-      <c r="A36" s="14" t="n">
+      <c r="A36" s="16" t="n">
         <v>21</v>
       </c>
       <c r="B36" s="8" t="inlineStr">
@@ -1157,7 +1170,7 @@
       <c r="G36" s="9" t="n"/>
     </row>
     <row r="37" ht="14.15" customHeight="1">
-      <c r="A37" s="14" t="n">
+      <c r="A37" s="16" t="n">
         <v>22</v>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -1181,7 +1194,7 @@
       <c r="G37" s="9" t="n"/>
     </row>
     <row r="38" ht="14.15" customHeight="1">
-      <c r="A38" s="14" t="n">
+      <c r="A38" s="16" t="n">
         <v>23</v>
       </c>
       <c r="B38" s="8" t="inlineStr">
@@ -1205,7 +1218,7 @@
       <c r="G38" s="9" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="17" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -1213,18 +1226,18 @@
       <c r="B39" s="11" t="n"/>
       <c r="C39" s="11" t="n"/>
       <c r="D39" s="12" t="n"/>
-      <c r="E39" s="15">
+      <c r="E39" s="17">
         <f>SUM(E16:E38)</f>
         <v/>
       </c>
-      <c r="F39" s="15">
+      <c r="F39" s="17">
         <f>SUM(F16:F38)</f>
         <v/>
       </c>
       <c r="G39" s="13" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="A40" s="17" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -1233,7 +1246,7 @@
       <c r="C40" s="11" t="n"/>
       <c r="D40" s="11" t="n"/>
       <c r="E40" s="12" t="n"/>
-      <c r="F40" s="15">
+      <c r="F40" s="17">
         <f>F39/E39*100</f>
         <v/>
       </c>
@@ -1241,7 +1254,7 @@
     </row>
     <row r="41" ht="9.75" customHeight="1"/>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr">
+      <c r="A42" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -1250,11 +1263,11 @@
       <c r="C42" s="11" t="n"/>
       <c r="D42" s="11" t="n"/>
       <c r="E42" s="12" t="n"/>
-      <c r="F42" s="15">
+      <c r="F42" s="17">
         <f>F40*30/100</f>
         <v/>
       </c>
-      <c r="G42" s="15" t="inlineStr">
+      <c r="G42" s="17" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -1353,7 +1366,10 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Classroom cum workshop – 500 - 600 sft (50-55 sqm)</t>
+          <t>Classroom – 350 sft (33 sqm)
+lab size – 500 sft (47 sqm)
+OR
+Classroom cum workshop – 500 sft (47 sqm)</t>
         </is>
       </c>
       <c r="D8" s="11" t="n"/>
@@ -1418,13 +1434,13 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="16" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Laptop/ Desktop (Minimum Intel core i5-i3 6 gen or AMD Ryzen 5), Ram: minimum 8 - 16 GB, Graphic Card: dedicated GPU 2GB, High Speed Internet (Minimum 10 Mbps), Graphic Design Software 
-(Photoshop CC, Illustrator CC, CorelDraw)</t>
+          <t>Laptop/ Desktop (Minimum Intel core i5 or Intel core i3 6 gen/above, or AMD Ryzen 5/ similar spec; Ram: minimum 8 - 16 GB; Display: FHD monitor; Graphic Card: dedicated GPU 2GB; High Speed Internet (Minimum 10 Mbps); Graphic Design Software 
+(Photoshop CC, Illustrator CC, InDesign, After Effects, CorelDraw); 3D Design Software (Blender, Cinema 4D or Autodesk Maya)</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
@@ -1443,7 +1459,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -1467,7 +1483,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="16" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -1491,7 +1507,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="16" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -1515,7 +1531,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -1539,7 +1555,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="16" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -1563,7 +1579,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -1587,16 +1603,16 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="16" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Air-conditioning (suited with workshop lab size)</t>
+          <t>Ergonomic chairs and desks (Plastic chairs/stool not acceptable)</t>
         </is>
       </c>
       <c r="C23" s="9" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D23" s="9" t="n">
         <v>0</v>
@@ -1610,96 +1626,80 @@
       </c>
       <c r="G23" s="9" t="n"/>
     </row>
-    <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="14" t="n">
-        <v>9</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Ergonomic chairs and desks (Plastic chairs/stool not acceptable)</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="n">
-        <v>26</v>
-      </c>
-      <c r="D24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F24" s="9">
-        <f>IFERROR(MIN(C24,D24)*E24/C24,0)</f>
-        <v/>
-      </c>
-      <c r="G24" s="9" t="n"/>
+    <row r="24">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="n"/>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="17">
+        <f>SUM(E16:E23)</f>
+        <v/>
+      </c>
+      <c r="F24" s="17">
+        <f>SUM(F16:F23)</f>
+        <v/>
+      </c>
+      <c r="G24" s="13" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>Sum</t>
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>Score out of 100</t>
         </is>
       </c>
       <c r="B25" s="11" t="n"/>
       <c r="C25" s="11" t="n"/>
-      <c r="D25" s="12" t="n"/>
-      <c r="E25" s="15">
-        <f>SUM(E16:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="15">
-        <f>SUM(F16:F24)</f>
+      <c r="D25" s="11" t="n"/>
+      <c r="E25" s="12" t="n"/>
+      <c r="F25" s="17">
+        <f>F24/E24*100</f>
         <v/>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>Score out of 100</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="n"/>
-      <c r="C26" s="11" t="n"/>
-      <c r="D26" s="11" t="n"/>
-      <c r="E26" s="12" t="n"/>
-      <c r="F26" s="15">
-        <f>F25/E25*100</f>
-        <v/>
-      </c>
-      <c r="G26" s="13" t="n"/>
-    </row>
-    <row r="27" ht="9.75" customHeight="1"/>
-    <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+    <row r="26" ht="9.75" customHeight="1"/>
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
       </c>
-      <c r="B28" s="11" t="n"/>
-      <c r="C28" s="11" t="n"/>
-      <c r="D28" s="11" t="n"/>
-      <c r="E28" s="12" t="n"/>
-      <c r="F28" s="15">
-        <f>F26*30/100</f>
-        <v/>
-      </c>
-      <c r="G28" s="15" t="inlineStr">
+      <c r="B27" s="11" t="n"/>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="11" t="n"/>
+      <c r="E27" s="12" t="n"/>
+      <c r="F27" s="17">
+        <f>F25*30/100</f>
+        <v/>
+      </c>
+      <c r="G27" s="17" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
       </c>
     </row>
+    <row r="28" ht="14.15" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>* For this course, the lab should be air-conditioned. Otherwise, the total points achieved will be halved.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A24:D24"/>
     <mergeCell ref="C8:G8"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:G28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1711,7 +1711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.17" customWidth="1" min="1" max="1"/>
@@ -1784,9 +1784,9 @@
       <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Classroom – 350 sft (33 sqm)
-Workshop/ lab – 800 sft (75 sqm)
-                     OR
-Classroom cum workshop – 1000 sft (93 sqm)</t>
+lab size – 500 sft (47 sqm)
+OR
+Classroom cum workshop – 500 sft (47 sqm)</t>
         </is>
       </c>
       <c r="D8" s="11" t="n"/>
@@ -1851,7 +1851,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="16" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -1875,7 +1875,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -1899,7 +1899,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="16" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -1923,7 +1923,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="16" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -1948,7 +1948,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -1973,13 +1973,13 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="16" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Tools: 
-Office application, photo editing software and video editing software</t>
+Office application, photo editing software and video editing software, SEO Tools, Social Media Management, Email Marketing, Content Creation, CRM, Data Entry, Affiliate Marketing, bid for job</t>
         </is>
       </c>
       <c r="C21" s="9" t="n">
@@ -1998,7 +1998,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -2022,12 +2022,12 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="16" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Internet connectivity with power back-up</t>
+          <t>Internet connectivity (Minimum 10 Mbps) with power back-up (at least 01 hour)</t>
         </is>
       </c>
       <c r="C23" s="9" t="n">
@@ -2046,7 +2046,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="17" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -2054,18 +2054,18 @@
       <c r="B24" s="11" t="n"/>
       <c r="C24" s="11" t="n"/>
       <c r="D24" s="12" t="n"/>
-      <c r="E24" s="15">
+      <c r="E24" s="17">
         <f>SUM(E16:E23)</f>
         <v/>
       </c>
-      <c r="F24" s="15">
+      <c r="F24" s="17">
         <f>SUM(F16:F23)</f>
         <v/>
       </c>
       <c r="G24" s="13" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="17" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -2074,7 +2074,7 @@
       <c r="C25" s="11" t="n"/>
       <c r="D25" s="11" t="n"/>
       <c r="E25" s="12" t="n"/>
-      <c r="F25" s="15">
+      <c r="F25" s="17">
         <f>F24/E24*100</f>
         <v/>
       </c>
@@ -2082,7 +2082,7 @@
     </row>
     <row r="26" ht="9.75" customHeight="1"/>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -2091,18 +2091,25 @@
       <c r="C27" s="11" t="n"/>
       <c r="D27" s="11" t="n"/>
       <c r="E27" s="12" t="n"/>
-      <c r="F27" s="15">
+      <c r="F27" s="17">
         <f>F25*30/100</f>
         <v/>
       </c>
-      <c r="G27" s="15" t="inlineStr">
+      <c r="G27" s="17" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
       </c>
     </row>
+    <row r="28" ht="14.15" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>* For this course, the lab should be air-conditioned. Otherwise, the total points achieved will be halved.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="A1:G1"/>
@@ -2111,6 +2118,7 @@
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:G28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2262,7 +2270,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="16" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -2286,7 +2294,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -2310,7 +2318,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="16" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -2334,7 +2342,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="16" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -2358,7 +2366,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -2382,7 +2390,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="16" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -2406,7 +2414,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -2430,7 +2438,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="16" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -2454,7 +2462,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="14" t="n">
+      <c r="A24" s="16" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -2478,7 +2486,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="14" t="n">
+      <c r="A25" s="16" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -2502,7 +2510,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="14" t="n">
+      <c r="A26" s="16" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -2526,7 +2534,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="14" t="n">
+      <c r="A27" s="16" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -2550,7 +2558,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="14" t="n">
+      <c r="A28" s="16" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -2574,7 +2582,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="14" t="n">
+      <c r="A29" s="16" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -2598,7 +2606,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="14" t="n">
+      <c r="A30" s="16" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -2622,7 +2630,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="14" t="n">
+      <c r="A31" s="16" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -2646,7 +2654,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="14" t="n">
+      <c r="A32" s="16" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -2670,7 +2678,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="14" t="n">
+      <c r="A33" s="16" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -2694,7 +2702,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="14" t="n">
+      <c r="A34" s="16" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -2718,7 +2726,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -2726,18 +2734,18 @@
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="12" t="n"/>
-      <c r="E35" s="15">
+      <c r="E35" s="17">
         <f>SUM(E16:E34)</f>
         <v/>
       </c>
-      <c r="F35" s="15">
+      <c r="F35" s="17">
         <f>SUM(F16:F34)</f>
         <v/>
       </c>
       <c r="G35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -2746,7 +2754,7 @@
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="12" t="n"/>
-      <c r="F36" s="15">
+      <c r="F36" s="17">
         <f>F35/E35*100</f>
         <v/>
       </c>
@@ -2754,7 +2762,7 @@
     </row>
     <row r="37" ht="9.75" customHeight="1"/>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -2763,11 +2771,11 @@
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="12" t="n"/>
-      <c r="F38" s="15">
+      <c r="F38" s="17">
         <f>F36*30/100</f>
         <v/>
       </c>
-      <c r="G38" s="15" t="inlineStr">
+      <c r="G38" s="17" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -2783,6 +2791,888 @@
     <mergeCell ref="A36:E36"/>
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="A37:G37"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15.17" customWidth="1" min="1" max="1"/>
+    <col width="33.13" customWidth="1" min="2" max="2"/>
+    <col width="13.72" customWidth="1" min="3" max="3"/>
+    <col width="13.72" customWidth="1" min="4" max="4"/>
+    <col width="13.72" customWidth="1" min="5" max="5"/>
+    <col width="13.72" customWidth="1" min="6" max="6"/>
+    <col width="13.72" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="17.35" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Course-wise Training Infrastructure and Facilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Course Name:</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Housekeeping</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26.85" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Number of Trainees:</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Course-wise Training Space (Theoretical Classroom, Workshop/ Lab/ Classroom cum Workshop)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Course Name</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>SICIP required space for 25 trainees</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="52.2" customHeight="1">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Housekeeping</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Classroom – minimum 350 sft. (33 sqm)
+Workshop/ lab – 800 sft. (75 sqm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Major Training Equipment and Training Facilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="115.65" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>•The institute shall not use the same facilities for any other projects/organizations offering a similar course.
+•The institute must provide sufficient evidence to prove ownership of the proposed training equipment.
+The list denotes the minimum training equipment and facility required to effectively conduct training for a specific course. Additionally, the institute must ensure that all other necessary training tools, equipment, and furniture are available to meet the requirement of competency standards (CS) provided by SICIP.
+For the operation of training course on Housekeeping, the institute must ensure the availability of at least 80% of the major training equipment and training facilities (according to the CS) to be eligible for SICIP training delivery. If the score is below 80%, the remaining equipment and facilities need to be installed before the commencement of the training.
+The institute will also provide all other hand tools and power tools as per CS for 25 trainees. Also, they will arrange adequate seating arrangement and classroom setup for the 25 trainees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26.85" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>S.N.</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Major Equipment and Training facilities</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Required facilities</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Available facilities</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Weights
+(out of 10)</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Weighted scores</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="14.15" customHeight="1">
+      <c r="A16" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Computers/Laptop</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" s="9">
+        <f>IFERROR(MIN(C16,D16)*E16/C16,0)</f>
+        <v/>
+      </c>
+      <c r="G16" s="9" t="n"/>
+    </row>
+    <row r="17" ht="14.15" customHeight="1">
+      <c r="A17" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Multimedia Projector</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" s="9">
+        <f>IFERROR(MIN(C17,D17)*E17/C17,0)</f>
+        <v/>
+      </c>
+      <c r="G17" s="9" t="n"/>
+    </row>
+    <row r="18" ht="14.15" customHeight="1">
+      <c r="A18" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Complete set up of hotel room with twin bed and side table</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="F18" s="9">
+        <f>IFERROR(MIN(C18,D18)*E18/C18,0)</f>
+        <v/>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>1 set</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="14.15" customHeight="1">
+      <c r="A19" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>A set of room materials comprising -
+Hospitality tray (drinking water, tea kettle, sugar, coffee, tea, creamer, milk, cup, glass, saucers, spoon), 
+Room directory 
+Room collateral (Do Not Disturb (DND)/Privacy Please and makeup sign, brochure, minibar price list, room service menu) 
+Note pad, Pen/Pencil
+Tissue box 
+Shoe horn
+Laundry bag 
+Slipper</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F19" s="9">
+        <f>IFERROR(MIN(C19,D19)*E19/C19,0)</f>
+        <v/>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>1 set</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="14.15" customHeight="1">
+      <c r="A20" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Bin Basket</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" s="9">
+        <f>IFERROR(MIN(C20,D20)*E20/C20,0)</f>
+        <v/>
+      </c>
+      <c r="G20" s="9" t="n"/>
+    </row>
+    <row r="21" ht="14.15" customHeight="1">
+      <c r="A21" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Complete set up of bathroom with bathtub</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="F21" s="9">
+        <f>IFERROR(MIN(C21,D21)*E21/C21,0)</f>
+        <v/>
+      </c>
+      <c r="G21" s="9" t="n"/>
+    </row>
+    <row r="22" ht="14.15" customHeight="1">
+      <c r="A22" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Bath room amenities: Soap (hand and bath), shampoo, Shower gel, Conditioner, Body lotion, Sanitary bag (women), Dental kit (Tooth paste and brush), Shaving kit, Loofa, Shower cap, Comb</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F22" s="9">
+        <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
+        <v/>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>1 set</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="14.15" customHeight="1">
+      <c r="A23" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Room attendant trolley</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F23" s="9">
+        <f>IFERROR(MIN(C23,D23)*E23/C23,0)</f>
+        <v/>
+      </c>
+      <c r="G23" s="9" t="n"/>
+    </row>
+    <row r="24" ht="14.15" customHeight="1">
+      <c r="A24" s="18" t="n">
+        <v>9</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Air-Conditioner</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" s="9">
+        <f>IFERROR(MIN(C24,D24)*E24/C24,0)</f>
+        <v/>
+      </c>
+      <c r="G24" s="9" t="n"/>
+    </row>
+    <row r="25" ht="14.15" customHeight="1">
+      <c r="A25" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Television (LED)</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F25" s="9">
+        <f>IFERROR(MIN(C25,D25)*E25/C25,0)</f>
+        <v/>
+      </c>
+      <c r="G25" s="9" t="n"/>
+    </row>
+    <row r="26" ht="14.15" customHeight="1">
+      <c r="A26" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Minibar</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" s="9">
+        <f>IFERROR(MIN(C26,D26)*E26/C26,0)</f>
+        <v/>
+      </c>
+      <c r="G26" s="9" t="n"/>
+    </row>
+    <row r="27" ht="14.15" customHeight="1">
+      <c r="A27" s="18" t="n">
+        <v>12</v>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Safe deposit box</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F27" s="9">
+        <f>IFERROR(MIN(C27,D27)*E27/C27,0)</f>
+        <v/>
+      </c>
+      <c r="G27" s="9" t="n"/>
+    </row>
+    <row r="28" ht="14.15" customHeight="1">
+      <c r="A28" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Cub board with three types of hangers</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" s="9">
+        <f>IFERROR(MIN(C28,D28)*E28/C28,0)</f>
+        <v/>
+      </c>
+      <c r="G28" s="9" t="n"/>
+    </row>
+    <row r="29" ht="14.15" customHeight="1">
+      <c r="A29" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Writing desk with chair</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F29" s="9">
+        <f>IFERROR(MIN(C29,D29)*E29/C29,0)</f>
+        <v/>
+      </c>
+      <c r="G29" s="9" t="n"/>
+    </row>
+    <row r="30" ht="14.15" customHeight="1">
+      <c r="A30" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Linens (Bed sheet, Duvet and cover, pillow with cover, bed runner and bed cushion)</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F30" s="9">
+        <f>IFERROR(MIN(C30,D30)*E30/C30,0)</f>
+        <v/>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>1 set</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="14.15" customHeight="1">
+      <c r="A31" s="18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Terry (Bath towel, hand towel, face towel, bath met and bathrobe)</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F31" s="9">
+        <f>IFERROR(MIN(C31,D31)*E31/C31,0)</f>
+        <v/>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>1 set</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="14.15" customHeight="1">
+      <c r="A32" s="18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Hand iron with board</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F32" s="9">
+        <f>IFERROR(MIN(C32,D32)*E32/C32,0)</f>
+        <v/>
+      </c>
+      <c r="G32" s="9" t="n"/>
+    </row>
+    <row r="33" ht="14.15" customHeight="1">
+      <c r="A33" s="18" t="n">
+        <v>18</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Hand Brush</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" s="9">
+        <f>IFERROR(MIN(C33,D33)*E33/C33,0)</f>
+        <v/>
+      </c>
+      <c r="G33" s="9" t="n"/>
+    </row>
+    <row r="34" ht="14.15" customHeight="1">
+      <c r="A34" s="18" t="n">
+        <v>19</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Bucket</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F34" s="9">
+        <f>IFERROR(MIN(C34,D34)*E34/C34,0)</f>
+        <v/>
+      </c>
+      <c r="G34" s="9" t="n"/>
+    </row>
+    <row r="35" ht="14.15" customHeight="1">
+      <c r="A35" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Telephone set</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F35" s="9">
+        <f>IFERROR(MIN(C35,D35)*E35/C35,0)</f>
+        <v/>
+      </c>
+      <c r="G35" s="9" t="n"/>
+    </row>
+    <row r="36" ht="14.15" customHeight="1">
+      <c r="A36" s="18" t="n">
+        <v>21</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Tub chair and coffee table</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F36" s="9">
+        <f>IFERROR(MIN(C36,D36)*E36/C36,0)</f>
+        <v/>
+      </c>
+      <c r="G36" s="9" t="n"/>
+    </row>
+    <row r="37" ht="14.15" customHeight="1">
+      <c r="A37" s="18" t="n">
+        <v>22</v>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Vacuum cleaner (wet and dry)</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F37" s="9">
+        <f>IFERROR(MIN(C37,D37)*E37/C37,0)</f>
+        <v/>
+      </c>
+      <c r="G37" s="9" t="n"/>
+    </row>
+    <row r="38" ht="14.15" customHeight="1">
+      <c r="A38" s="18" t="n">
+        <v>23</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Glass wiper (short/long)</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F38" s="9">
+        <f>IFERROR(MIN(C38,D38)*E38/C38,0)</f>
+        <v/>
+      </c>
+      <c r="G38" s="9" t="n"/>
+    </row>
+    <row r="39" ht="14.15" customHeight="1">
+      <c r="A39" s="18" t="n">
+        <v>24</v>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>Squeezer (short/long)</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F39" s="9">
+        <f>IFERROR(MIN(C39,D39)*E39/C39,0)</f>
+        <v/>
+      </c>
+      <c r="G39" s="9" t="n"/>
+    </row>
+    <row r="40" ht="14.15" customHeight="1">
+      <c r="A40" s="18" t="n">
+        <v>25</v>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Ladder</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F40" s="9">
+        <f>IFERROR(MIN(C40,D40)*E40/C40,0)</f>
+        <v/>
+      </c>
+      <c r="G40" s="9" t="n"/>
+    </row>
+    <row r="41" ht="14.15" customHeight="1">
+      <c r="A41" s="18" t="n">
+        <v>26</v>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Hand caddie box</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F41" s="9">
+        <f>IFERROR(MIN(C41,D41)*E41/C41,0)</f>
+        <v/>
+      </c>
+      <c r="G41" s="9" t="n"/>
+    </row>
+    <row r="42" ht="14.15" customHeight="1">
+      <c r="A42" s="18" t="n">
+        <v>27</v>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Prayer mat</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" s="9">
+        <f>IFERROR(MIN(C42,D42)*E42/C42,0)</f>
+        <v/>
+      </c>
+      <c r="G42" s="9" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="n"/>
+      <c r="C43" s="11" t="n"/>
+      <c r="D43" s="12" t="n"/>
+      <c r="E43" s="19">
+        <f>SUM(E16:E42)</f>
+        <v/>
+      </c>
+      <c r="F43" s="19">
+        <f>SUM(F16:F42)</f>
+        <v/>
+      </c>
+      <c r="G43" s="13" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>Score out of 100</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="n"/>
+      <c r="C44" s="11" t="n"/>
+      <c r="D44" s="11" t="n"/>
+      <c r="E44" s="12" t="n"/>
+      <c r="F44" s="19">
+        <f>F43/E43*100</f>
+        <v/>
+      </c>
+      <c r="G44" s="13" t="n"/>
+    </row>
+    <row r="45" ht="9.75" customHeight="1"/>
+    <row r="46">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total achieved points out of 30  </t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="n"/>
+      <c r="C46" s="11" t="n"/>
+      <c r="D46" s="11" t="n"/>
+      <c r="E46" s="12" t="n"/>
+      <c r="F46" s="19">
+        <f>F44*30/100</f>
+        <v/>
+      </c>
+      <c r="G46" s="19" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="A45:G45"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2933,7 +3823,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="16" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -2957,7 +3847,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -2981,7 +3871,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="16" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -3005,7 +3895,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="16" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -3029,7 +3919,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -3053,7 +3943,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="16" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -3077,7 +3967,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -3101,7 +3991,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="16" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -3125,7 +4015,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="14" t="n">
+      <c r="A24" s="16" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -3149,7 +4039,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="14" t="n">
+      <c r="A25" s="16" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -3173,7 +4063,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="14" t="n">
+      <c r="A26" s="16" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -3197,7 +4087,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="14" t="n">
+      <c r="A27" s="16" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -3221,7 +4111,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="14" t="n">
+      <c r="A28" s="16" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -3245,7 +4135,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="14" t="n">
+      <c r="A29" s="16" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -3269,7 +4159,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="14" t="n">
+      <c r="A30" s="16" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -3293,7 +4183,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="14" t="n">
+      <c r="A31" s="16" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -3317,7 +4207,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="14" t="n">
+      <c r="A32" s="16" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -3341,7 +4231,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="14" t="n">
+      <c r="A33" s="16" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -3365,7 +4255,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="14" t="n">
+      <c r="A34" s="16" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -3389,7 +4279,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -3397,18 +4287,18 @@
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="12" t="n"/>
-      <c r="E35" s="15">
+      <c r="E35" s="17">
         <f>SUM(E16:E34)</f>
         <v/>
       </c>
-      <c r="F35" s="15">
+      <c r="F35" s="17">
         <f>SUM(F16:F34)</f>
         <v/>
       </c>
       <c r="G35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -3417,7 +4307,7 @@
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="12" t="n"/>
-      <c r="F36" s="15">
+      <c r="F36" s="17">
         <f>F35/E35*100</f>
         <v/>
       </c>
@@ -3425,7 +4315,7 @@
     </row>
     <row r="37" ht="9.75" customHeight="1"/>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -3434,11 +4324,11 @@
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="12" t="n"/>
-      <c r="F38" s="15">
+      <c r="F38" s="17">
         <f>F36*30/100</f>
         <v/>
       </c>
-      <c r="G38" s="15" t="inlineStr">
+      <c r="G38" s="17" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -3465,7 +4355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.17" customWidth="1" min="1" max="1"/>
@@ -3538,9 +4428,9 @@
       <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Classroom – 350 sft (33 sqm)
-Workshop/ lab – 800 sft (75 sqm)
-                     OR
-Classroom cum workshop – 1000 sft (93 sqm)</t>
+lab size – 500 sft (47 sqm)
+OR
+Classroom cum workshop – 500 sft (47 sqm)</t>
         </is>
       </c>
       <c r="D8" s="11" t="n"/>
@@ -3605,7 +4495,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="16" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -3629,7 +4519,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -3653,7 +4543,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="16" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -3677,7 +4567,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="16" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -3702,7 +4592,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -3727,13 +4617,13 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="16" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Tools: 
-Office application, photo editing software and video editing software</t>
+Office application, photo editing software and video editing software, SEO Tools, Social Media Management, Email Marketing, Content Creation, CRM, ad campaigns</t>
         </is>
       </c>
       <c r="C21" s="9" t="n">
@@ -3752,7 +4642,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -3776,12 +4666,12 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="16" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Internet connectivity with power back-up</t>
+          <t>Internet connectivity (Minimum 10 Mbps) with power back-up (at least 01 hour)</t>
         </is>
       </c>
       <c r="C23" s="9" t="n">
@@ -3800,7 +4690,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="17" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -3808,18 +4698,18 @@
       <c r="B24" s="11" t="n"/>
       <c r="C24" s="11" t="n"/>
       <c r="D24" s="12" t="n"/>
-      <c r="E24" s="15">
+      <c r="E24" s="17">
         <f>SUM(E16:E23)</f>
         <v/>
       </c>
-      <c r="F24" s="15">
+      <c r="F24" s="17">
         <f>SUM(F16:F23)</f>
         <v/>
       </c>
       <c r="G24" s="13" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="17" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -3828,7 +4718,7 @@
       <c r="C25" s="11" t="n"/>
       <c r="D25" s="11" t="n"/>
       <c r="E25" s="12" t="n"/>
-      <c r="F25" s="15">
+      <c r="F25" s="17">
         <f>F24/E24*100</f>
         <v/>
       </c>
@@ -3836,7 +4726,7 @@
     </row>
     <row r="26" ht="9.75" customHeight="1"/>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -3845,18 +4735,25 @@
       <c r="C27" s="11" t="n"/>
       <c r="D27" s="11" t="n"/>
       <c r="E27" s="12" t="n"/>
-      <c r="F27" s="15">
+      <c r="F27" s="17">
         <f>F25*30/100</f>
         <v/>
       </c>
-      <c r="G27" s="15" t="inlineStr">
+      <c r="G27" s="17" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
       </c>
     </row>
+    <row r="28" ht="14.15" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>* For this course, the lab should be air-conditioned. Otherwise, the total points achieved will be halved.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="A1:G1"/>
@@ -3865,6 +4762,7 @@
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:G28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4015,7 +4913,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="16" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -4039,7 +4937,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -4063,7 +4961,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="16" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -4087,7 +4985,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="16" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -4111,7 +5009,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -4135,7 +5033,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="16" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -4159,7 +5057,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -4183,7 +5081,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="16" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -4207,7 +5105,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="14" t="n">
+      <c r="A24" s="16" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -4231,7 +5129,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="14" t="n">
+      <c r="A25" s="16" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -4255,7 +5153,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="14" t="n">
+      <c r="A26" s="16" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -4279,7 +5177,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="14" t="n">
+      <c r="A27" s="16" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -4303,7 +5201,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="14" t="n">
+      <c r="A28" s="16" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -4327,7 +5225,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="14" t="n">
+      <c r="A29" s="16" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -4351,7 +5249,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="14" t="n">
+      <c r="A30" s="16" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -4375,7 +5273,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="14" t="n">
+      <c r="A31" s="16" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -4399,7 +5297,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="14" t="n">
+      <c r="A32" s="16" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -4423,7 +5321,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="14" t="n">
+      <c r="A33" s="16" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -4447,7 +5345,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="14" t="n">
+      <c r="A34" s="16" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -4471,7 +5369,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35" ht="14.15" customHeight="1">
-      <c r="A35" s="14" t="n">
+      <c r="A35" s="16" t="n">
         <v>20</v>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -4495,7 +5393,7 @@
       <c r="G35" s="9" t="n"/>
     </row>
     <row r="36" ht="14.15" customHeight="1">
-      <c r="A36" s="14" t="n">
+      <c r="A36" s="16" t="n">
         <v>21</v>
       </c>
       <c r="B36" s="8" t="inlineStr">
@@ -4519,7 +5417,7 @@
       <c r="G36" s="9" t="n"/>
     </row>
     <row r="37" ht="14.15" customHeight="1">
-      <c r="A37" s="14" t="n">
+      <c r="A37" s="16" t="n">
         <v>22</v>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -4543,7 +5441,7 @@
       <c r="G37" s="9" t="n"/>
     </row>
     <row r="38" ht="14.15" customHeight="1">
-      <c r="A38" s="14" t="n">
+      <c r="A38" s="16" t="n">
         <v>23</v>
       </c>
       <c r="B38" s="8" t="inlineStr">
@@ -4567,7 +5465,7 @@
       <c r="G38" s="9" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="17" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -4575,18 +5473,18 @@
       <c r="B39" s="11" t="n"/>
       <c r="C39" s="11" t="n"/>
       <c r="D39" s="12" t="n"/>
-      <c r="E39" s="15">
+      <c r="E39" s="17">
         <f>SUM(E16:E38)</f>
         <v/>
       </c>
-      <c r="F39" s="15">
+      <c r="F39" s="17">
         <f>SUM(F16:F38)</f>
         <v/>
       </c>
       <c r="G39" s="13" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="A40" s="17" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -4595,7 +5493,7 @@
       <c r="C40" s="11" t="n"/>
       <c r="D40" s="11" t="n"/>
       <c r="E40" s="12" t="n"/>
-      <c r="F40" s="15">
+      <c r="F40" s="17">
         <f>F39/E39*100</f>
         <v/>
       </c>
@@ -4603,7 +5501,7 @@
     </row>
     <row r="41" ht="9.75" customHeight="1"/>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr">
+      <c r="A42" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -4612,11 +5510,11 @@
       <c r="C42" s="11" t="n"/>
       <c r="D42" s="11" t="n"/>
       <c r="E42" s="12" t="n"/>
-      <c r="F42" s="15">
+      <c r="F42" s="17">
         <f>F40*30/100</f>
         <v/>
       </c>
-      <c r="G42" s="15" t="inlineStr">
+      <c r="G42" s="17" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -4782,7 +5680,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="16" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -4806,7 +5704,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -4830,7 +5728,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="16" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -4854,7 +5752,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="16" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -4878,7 +5776,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -4902,7 +5800,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="16" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -4926,7 +5824,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -4950,7 +5848,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="16" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -4974,7 +5872,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="14" t="n">
+      <c r="A24" s="16" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -4998,7 +5896,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="14" t="n">
+      <c r="A25" s="16" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -5022,7 +5920,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="14" t="n">
+      <c r="A26" s="16" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -5046,7 +5944,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="14" t="n">
+      <c r="A27" s="16" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -5070,7 +5968,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="14" t="n">
+      <c r="A28" s="16" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -5094,7 +5992,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="14" t="n">
+      <c r="A29" s="16" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -5118,7 +6016,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="14" t="n">
+      <c r="A30" s="16" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -5142,7 +6040,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="14" t="n">
+      <c r="A31" s="16" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -5166,7 +6064,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="14" t="n">
+      <c r="A32" s="16" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -5190,7 +6088,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="14" t="n">
+      <c r="A33" s="16" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -5214,7 +6112,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" s="17" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -5222,18 +6120,18 @@
       <c r="B34" s="11" t="n"/>
       <c r="C34" s="11" t="n"/>
       <c r="D34" s="12" t="n"/>
-      <c r="E34" s="15">
+      <c r="E34" s="17">
         <f>SUM(E16:E33)</f>
         <v/>
       </c>
-      <c r="F34" s="15">
+      <c r="F34" s="17">
         <f>SUM(F16:F33)</f>
         <v/>
       </c>
       <c r="G34" s="13" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -5242,7 +6140,7 @@
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="11" t="n"/>
       <c r="E35" s="12" t="n"/>
-      <c r="F35" s="15">
+      <c r="F35" s="17">
         <f>F34/E34*100</f>
         <v/>
       </c>
@@ -5250,7 +6148,7 @@
     </row>
     <row r="36" ht="9.75" customHeight="1"/>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -5259,11 +6157,11 @@
       <c r="C37" s="11" t="n"/>
       <c r="D37" s="11" t="n"/>
       <c r="E37" s="12" t="n"/>
-      <c r="F37" s="15">
+      <c r="F37" s="17">
         <f>F35*30/100</f>
         <v/>
       </c>
-      <c r="G37" s="15" t="inlineStr">
+      <c r="G37" s="17" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -5429,7 +6327,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="16" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -5453,7 +6351,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -5477,7 +6375,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="16" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -5501,7 +6399,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="16" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -5525,7 +6423,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -5549,7 +6447,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="16" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -5573,7 +6471,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -5597,7 +6495,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="16" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -5621,7 +6519,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="14" t="n">
+      <c r="A24" s="16" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -5645,7 +6543,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="14" t="n">
+      <c r="A25" s="16" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -5669,7 +6567,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="14" t="n">
+      <c r="A26" s="16" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -5693,7 +6591,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="14" t="n">
+      <c r="A27" s="16" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -5717,7 +6615,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="14" t="n">
+      <c r="A28" s="16" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -5741,7 +6639,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="14" t="n">
+      <c r="A29" s="16" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -5765,7 +6663,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="14" t="n">
+      <c r="A30" s="16" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -5789,7 +6687,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="14" t="n">
+      <c r="A31" s="16" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -5813,7 +6711,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="14" t="n">
+      <c r="A32" s="16" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -5837,7 +6735,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="14" t="n">
+      <c r="A33" s="16" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -5861,7 +6759,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="14" t="n">
+      <c r="A34" s="16" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -5885,7 +6783,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35" ht="14.15" customHeight="1">
-      <c r="A35" s="14" t="n">
+      <c r="A35" s="16" t="n">
         <v>20</v>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -5909,7 +6807,7 @@
       <c r="G35" s="9" t="n"/>
     </row>
     <row r="36" ht="14.15" customHeight="1">
-      <c r="A36" s="14" t="n">
+      <c r="A36" s="16" t="n">
         <v>21</v>
       </c>
       <c r="B36" s="8" t="inlineStr">
@@ -5933,7 +6831,7 @@
       <c r="G36" s="9" t="n"/>
     </row>
     <row r="37" ht="14.15" customHeight="1">
-      <c r="A37" s="14" t="n">
+      <c r="A37" s="16" t="n">
         <v>22</v>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -5957,7 +6855,7 @@
       <c r="G37" s="9" t="n"/>
     </row>
     <row r="38" ht="14.15" customHeight="1">
-      <c r="A38" s="14" t="n">
+      <c r="A38" s="16" t="n">
         <v>23</v>
       </c>
       <c r="B38" s="8" t="inlineStr">
@@ -5981,7 +6879,7 @@
       <c r="G38" s="9" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="17" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -5989,18 +6887,18 @@
       <c r="B39" s="11" t="n"/>
       <c r="C39" s="11" t="n"/>
       <c r="D39" s="12" t="n"/>
-      <c r="E39" s="15">
+      <c r="E39" s="17">
         <f>SUM(E16:E38)</f>
         <v/>
       </c>
-      <c r="F39" s="15">
+      <c r="F39" s="17">
         <f>SUM(F16:F38)</f>
         <v/>
       </c>
       <c r="G39" s="13" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="A40" s="17" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -6009,7 +6907,7 @@
       <c r="C40" s="11" t="n"/>
       <c r="D40" s="11" t="n"/>
       <c r="E40" s="12" t="n"/>
-      <c r="F40" s="15">
+      <c r="F40" s="17">
         <f>F39/E39*100</f>
         <v/>
       </c>
@@ -6017,7 +6915,7 @@
     </row>
     <row r="41" ht="9.75" customHeight="1"/>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr">
+      <c r="A42" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -6026,11 +6924,11 @@
       <c r="C42" s="11" t="n"/>
       <c r="D42" s="11" t="n"/>
       <c r="E42" s="12" t="n"/>
-      <c r="F42" s="15">
+      <c r="F42" s="17">
         <f>F40*30/100</f>
         <v/>
       </c>
-      <c r="G42" s="15" t="inlineStr">
+      <c r="G42" s="17" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -6197,7 +7095,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="16" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -6221,7 +7119,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -6245,7 +7143,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="16" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -6269,7 +7167,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="16" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -6293,7 +7191,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -6317,7 +7215,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="16" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -6341,7 +7239,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -6365,7 +7263,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="16" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -6389,7 +7287,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="14" t="n">
+      <c r="A24" s="16" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -6413,7 +7311,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="14" t="n">
+      <c r="A25" s="16" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -6437,7 +7335,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="14" t="n">
+      <c r="A26" s="16" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -6461,7 +7359,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="14" t="n">
+      <c r="A27" s="16" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -6485,7 +7383,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="14" t="n">
+      <c r="A28" s="16" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -6509,7 +7407,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="14" t="n">
+      <c r="A29" s="16" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -6533,7 +7431,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="14" t="n">
+      <c r="A30" s="16" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -6557,7 +7455,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="14" t="n">
+      <c r="A31" s="16" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -6581,7 +7479,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="14" t="n">
+      <c r="A32" s="16" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -6605,7 +7503,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="14" t="n">
+      <c r="A33" s="16" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -6629,7 +7527,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="14" t="n">
+      <c r="A34" s="16" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -6653,7 +7551,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35" ht="14.15" customHeight="1">
-      <c r="A35" s="14" t="n">
+      <c r="A35" s="16" t="n">
         <v>20</v>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -6677,7 +7575,7 @@
       <c r="G35" s="9" t="n"/>
     </row>
     <row r="36" ht="14.15" customHeight="1">
-      <c r="A36" s="14" t="n">
+      <c r="A36" s="16" t="n">
         <v>21</v>
       </c>
       <c r="B36" s="8" t="inlineStr">
@@ -6701,7 +7599,7 @@
       <c r="G36" s="9" t="n"/>
     </row>
     <row r="37" ht="14.15" customHeight="1">
-      <c r="A37" s="14" t="n">
+      <c r="A37" s="16" t="n">
         <v>22</v>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -6725,7 +7623,7 @@
       <c r="G37" s="9" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -6733,18 +7631,18 @@
       <c r="B38" s="11" t="n"/>
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="12" t="n"/>
-      <c r="E38" s="15">
+      <c r="E38" s="17">
         <f>SUM(E16:E37)</f>
         <v/>
       </c>
-      <c r="F38" s="15">
+      <c r="F38" s="17">
         <f>SUM(F16:F37)</f>
         <v/>
       </c>
       <c r="G38" s="13" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="17" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -6753,7 +7651,7 @@
       <c r="C39" s="11" t="n"/>
       <c r="D39" s="11" t="n"/>
       <c r="E39" s="12" t="n"/>
-      <c r="F39" s="15">
+      <c r="F39" s="17">
         <f>F38/E38*100</f>
         <v/>
       </c>
@@ -6761,7 +7659,7 @@
     </row>
     <row r="40" ht="9.75" customHeight="1"/>
     <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="A41" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -6770,11 +7668,11 @@
       <c r="C41" s="11" t="n"/>
       <c r="D41" s="11" t="n"/>
       <c r="E41" s="12" t="n"/>
-      <c r="F41" s="15">
+      <c r="F41" s="17">
         <f>F39*30/100</f>
         <v/>
       </c>
-      <c r="G41" s="15" t="inlineStr">
+      <c r="G41" s="17" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -6940,7 +7838,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="16" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -6964,7 +7862,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -6988,7 +7886,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="16" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -7012,7 +7910,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="16" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -7036,7 +7934,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -7060,7 +7958,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="16" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -7084,7 +7982,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -7108,7 +8006,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="16" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -7132,7 +8030,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="14" t="n">
+      <c r="A24" s="16" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -7156,7 +8054,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="14" t="n">
+      <c r="A25" s="16" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -7180,7 +8078,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="14" t="n">
+      <c r="A26" s="16" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -7204,7 +8102,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="14" t="n">
+      <c r="A27" s="16" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -7228,7 +8126,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="14" t="n">
+      <c r="A28" s="16" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -7252,7 +8150,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="14" t="n">
+      <c r="A29" s="16" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -7276,7 +8174,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="14" t="n">
+      <c r="A30" s="16" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -7300,7 +8198,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="14" t="n">
+      <c r="A31" s="16" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -7324,7 +8222,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="14" t="n">
+      <c r="A32" s="16" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -7348,7 +8246,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="14" t="n">
+      <c r="A33" s="16" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -7372,7 +8270,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="14" t="n">
+      <c r="A34" s="16" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -7396,7 +8294,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35" ht="14.15" customHeight="1">
-      <c r="A35" s="14" t="n">
+      <c r="A35" s="16" t="n">
         <v>20</v>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -7420,7 +8318,7 @@
       <c r="G35" s="9" t="n"/>
     </row>
     <row r="36" ht="14.15" customHeight="1">
-      <c r="A36" s="14" t="n">
+      <c r="A36" s="16" t="n">
         <v>21</v>
       </c>
       <c r="B36" s="8" t="inlineStr">
@@ -7444,7 +8342,7 @@
       <c r="G36" s="9" t="n"/>
     </row>
     <row r="37" ht="14.15" customHeight="1">
-      <c r="A37" s="14" t="n">
+      <c r="A37" s="16" t="n">
         <v>22</v>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -7468,7 +8366,7 @@
       <c r="G37" s="9" t="n"/>
     </row>
     <row r="38" ht="14.15" customHeight="1">
-      <c r="A38" s="14" t="n">
+      <c r="A38" s="16" t="n">
         <v>23</v>
       </c>
       <c r="B38" s="8" t="inlineStr">
@@ -7492,7 +8390,7 @@
       <c r="G38" s="9" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="17" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -7500,18 +8398,18 @@
       <c r="B39" s="11" t="n"/>
       <c r="C39" s="11" t="n"/>
       <c r="D39" s="12" t="n"/>
-      <c r="E39" s="15">
+      <c r="E39" s="17">
         <f>SUM(E16:E38)</f>
         <v/>
       </c>
-      <c r="F39" s="15">
+      <c r="F39" s="17">
         <f>SUM(F16:F38)</f>
         <v/>
       </c>
       <c r="G39" s="13" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="A40" s="17" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -7520,7 +8418,7 @@
       <c r="C40" s="11" t="n"/>
       <c r="D40" s="11" t="n"/>
       <c r="E40" s="12" t="n"/>
-      <c r="F40" s="15">
+      <c r="F40" s="17">
         <f>F39/E39*100</f>
         <v/>
       </c>
@@ -7528,7 +8426,7 @@
     </row>
     <row r="41" ht="9.75" customHeight="1"/>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr">
+      <c r="A42" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -7537,11 +8435,11 @@
       <c r="C42" s="11" t="n"/>
       <c r="D42" s="11" t="n"/>
       <c r="E42" s="12" t="n"/>
-      <c r="F42" s="15">
+      <c r="F42" s="17">
         <f>F40*30/100</f>
         <v/>
       </c>
-      <c r="G42" s="15" t="inlineStr">
+      <c r="G42" s="17" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -7706,7 +8604,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="16" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -7730,7 +8628,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -7754,7 +8652,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="16" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -7778,7 +8676,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="16" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -7802,7 +8700,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -7826,7 +8724,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="16" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -7850,7 +8748,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -7874,7 +8772,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="16" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -7898,7 +8796,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="14" t="n">
+      <c r="A24" s="16" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -7922,7 +8820,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="14" t="n">
+      <c r="A25" s="16" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -7946,7 +8844,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="14" t="n">
+      <c r="A26" s="16" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -7970,7 +8868,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="14" t="n">
+      <c r="A27" s="16" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -7994,7 +8892,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="14" t="n">
+      <c r="A28" s="16" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -8018,7 +8916,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="14" t="n">
+      <c r="A29" s="16" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -8042,7 +8940,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="14" t="n">
+      <c r="A30" s="16" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -8066,7 +8964,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="14" t="n">
+      <c r="A31" s="16" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -8090,7 +8988,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="14" t="n">
+      <c r="A32" s="16" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -8114,7 +9012,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="14" t="n">
+      <c r="A33" s="16" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -8138,7 +9036,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" s="17" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -8146,18 +9044,18 @@
       <c r="B34" s="11" t="n"/>
       <c r="C34" s="11" t="n"/>
       <c r="D34" s="12" t="n"/>
-      <c r="E34" s="15">
+      <c r="E34" s="17">
         <f>SUM(E16:E33)</f>
         <v/>
       </c>
-      <c r="F34" s="15">
+      <c r="F34" s="17">
         <f>SUM(F16:F33)</f>
         <v/>
       </c>
       <c r="G34" s="13" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -8166,7 +9064,7 @@
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="11" t="n"/>
       <c r="E35" s="12" t="n"/>
-      <c r="F35" s="15">
+      <c r="F35" s="17">
         <f>F34/E34*100</f>
         <v/>
       </c>
@@ -8174,7 +9072,7 @@
     </row>
     <row r="36" ht="9.75" customHeight="1"/>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -8183,11 +9081,11 @@
       <c r="C37" s="11" t="n"/>
       <c r="D37" s="11" t="n"/>
       <c r="E37" s="12" t="n"/>
-      <c r="F37" s="15">
+      <c r="F37" s="17">
         <f>F35*30/100</f>
         <v/>
       </c>
-      <c r="G37" s="15" t="inlineStr">
+      <c r="G37" s="17" t="inlineStr">
         <is>
           <t>Points</t>
         </is>

--- a/lab-standards/PKSF-lab-standard.xlsx
+++ b/lab-standards/PKSF-lab-standard.xlsx
@@ -666,7 +666,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="16" t="n">
+      <c r="A16" s="18" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -690,7 +690,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="16" t="n">
+      <c r="A17" s="18" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -714,7 +714,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="16" t="n">
+      <c r="A18" s="18" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -738,7 +738,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="16" t="n">
+      <c r="A19" s="18" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -762,7 +762,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="16" t="n">
+      <c r="A20" s="18" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -786,7 +786,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="16" t="n">
+      <c r="A21" s="18" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -810,7 +810,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="16" t="n">
+      <c r="A22" s="18" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -834,7 +834,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="16" t="n">
+      <c r="A23" s="18" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -858,7 +858,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="16" t="n">
+      <c r="A24" s="18" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -882,7 +882,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="16" t="n">
+      <c r="A25" s="18" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -906,7 +906,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="16" t="n">
+      <c r="A26" s="18" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -930,7 +930,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="16" t="n">
+      <c r="A27" s="18" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -954,7 +954,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="16" t="n">
+      <c r="A28" s="18" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -978,7 +978,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="16" t="n">
+      <c r="A29" s="18" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -1002,7 +1002,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="16" t="n">
+      <c r="A30" s="18" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -1026,7 +1026,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="16" t="n">
+      <c r="A31" s="18" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -1050,7 +1050,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="16" t="n">
+      <c r="A32" s="18" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -1074,7 +1074,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="16" t="n">
+      <c r="A33" s="18" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -1098,7 +1098,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="16" t="n">
+      <c r="A34" s="18" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -1122,7 +1122,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35" ht="14.15" customHeight="1">
-      <c r="A35" s="16" t="n">
+      <c r="A35" s="18" t="n">
         <v>20</v>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -1146,7 +1146,7 @@
       <c r="G35" s="9" t="n"/>
     </row>
     <row r="36" ht="14.15" customHeight="1">
-      <c r="A36" s="16" t="n">
+      <c r="A36" s="18" t="n">
         <v>21</v>
       </c>
       <c r="B36" s="8" t="inlineStr">
@@ -1170,7 +1170,7 @@
       <c r="G36" s="9" t="n"/>
     </row>
     <row r="37" ht="14.15" customHeight="1">
-      <c r="A37" s="16" t="n">
+      <c r="A37" s="18" t="n">
         <v>22</v>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -1194,7 +1194,7 @@
       <c r="G37" s="9" t="n"/>
     </row>
     <row r="38" ht="14.15" customHeight="1">
-      <c r="A38" s="16" t="n">
+      <c r="A38" s="18" t="n">
         <v>23</v>
       </c>
       <c r="B38" s="8" t="inlineStr">
@@ -1218,7 +1218,7 @@
       <c r="G38" s="9" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="17" t="inlineStr">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -1226,18 +1226,18 @@
       <c r="B39" s="11" t="n"/>
       <c r="C39" s="11" t="n"/>
       <c r="D39" s="12" t="n"/>
-      <c r="E39" s="17">
+      <c r="E39" s="19">
         <f>SUM(E16:E38)</f>
         <v/>
       </c>
-      <c r="F39" s="17">
+      <c r="F39" s="19">
         <f>SUM(F16:F38)</f>
         <v/>
       </c>
       <c r="G39" s="13" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="17" t="inlineStr">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -1246,7 +1246,7 @@
       <c r="C40" s="11" t="n"/>
       <c r="D40" s="11" t="n"/>
       <c r="E40" s="12" t="n"/>
-      <c r="F40" s="17">
+      <c r="F40" s="19">
         <f>F39/E39*100</f>
         <v/>
       </c>
@@ -1254,7 +1254,7 @@
     </row>
     <row r="41" ht="9.75" customHeight="1"/>
     <row r="42">
-      <c r="A42" s="17" t="inlineStr">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -1263,11 +1263,11 @@
       <c r="C42" s="11" t="n"/>
       <c r="D42" s="11" t="n"/>
       <c r="E42" s="12" t="n"/>
-      <c r="F42" s="17">
+      <c r="F42" s="19">
         <f>F40*30/100</f>
         <v/>
       </c>
-      <c r="G42" s="17" t="inlineStr">
+      <c r="G42" s="19" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -1434,7 +1434,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="16" t="n">
+      <c r="A16" s="18" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -1459,7 +1459,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="16" t="n">
+      <c r="A17" s="18" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -1483,7 +1483,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="16" t="n">
+      <c r="A18" s="18" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -1507,7 +1507,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="16" t="n">
+      <c r="A19" s="18" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -1531,7 +1531,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="16" t="n">
+      <c r="A20" s="18" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -1555,7 +1555,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="16" t="n">
+      <c r="A21" s="18" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -1579,7 +1579,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="16" t="n">
+      <c r="A22" s="18" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -1603,7 +1603,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="16" t="n">
+      <c r="A23" s="18" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -1627,7 +1627,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -1635,18 +1635,18 @@
       <c r="B24" s="11" t="n"/>
       <c r="C24" s="11" t="n"/>
       <c r="D24" s="12" t="n"/>
-      <c r="E24" s="17">
+      <c r="E24" s="19">
         <f>SUM(E16:E23)</f>
         <v/>
       </c>
-      <c r="F24" s="17">
+      <c r="F24" s="19">
         <f>SUM(F16:F23)</f>
         <v/>
       </c>
       <c r="G24" s="13" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -1655,7 +1655,7 @@
       <c r="C25" s="11" t="n"/>
       <c r="D25" s="11" t="n"/>
       <c r="E25" s="12" t="n"/>
-      <c r="F25" s="17">
+      <c r="F25" s="19">
         <f>F24/E24*100</f>
         <v/>
       </c>
@@ -1663,7 +1663,7 @@
     </row>
     <row r="26" ht="9.75" customHeight="1"/>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -1672,11 +1672,11 @@
       <c r="C27" s="11" t="n"/>
       <c r="D27" s="11" t="n"/>
       <c r="E27" s="12" t="n"/>
-      <c r="F27" s="17">
+      <c r="F27" s="19">
         <f>F25*30/100</f>
         <v/>
       </c>
-      <c r="G27" s="17" t="inlineStr">
+      <c r="G27" s="19" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -1730,6 +1730,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1752,6 +1753,7 @@
         <v>25</v>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -1794,6 +1796,8 @@
       <c r="F8" s="11" t="n"/>
       <c r="G8" s="12" t="n"/>
     </row>
+    <row r="9"/>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
@@ -1801,6 +1805,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="115.65" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -1812,6 +1817,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="26.85" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
@@ -1851,7 +1857,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="16" t="n">
+      <c r="A16" s="18" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -1875,7 +1881,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="16" t="n">
+      <c r="A17" s="18" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -1899,7 +1905,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="16" t="n">
+      <c r="A18" s="18" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -1923,13 +1929,13 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="16" t="n">
+      <c r="A19" s="18" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Computers/Laptop: 
-(Minimum Intel Core i5 processor (8th Gen), 8GB RAM (16GB preferred), 500GB SSD storage (1TB preferred), High-resolution monitors (19/20-inch minimum, with color accuracy).</t>
+(Minimum Intel core i5 or Intel core i3 6 gen/above, or AMD similar spec, 8GB RAM (16GB preferred), 500GB SSD storage (1TB preferred), High-resolution monitors (19/20-inch minimum, with color accuracy).</t>
         </is>
       </c>
       <c r="C19" s="9" t="n">
@@ -1948,7 +1954,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="16" t="n">
+      <c r="A20" s="18" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -1973,7 +1979,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="16" t="n">
+      <c r="A21" s="18" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -1998,7 +2004,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="16" t="n">
+      <c r="A22" s="18" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -2022,7 +2028,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="16" t="n">
+      <c r="A23" s="18" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -2046,7 +2052,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -2054,18 +2060,18 @@
       <c r="B24" s="11" t="n"/>
       <c r="C24" s="11" t="n"/>
       <c r="D24" s="12" t="n"/>
-      <c r="E24" s="17">
+      <c r="E24" s="19">
         <f>SUM(E16:E23)</f>
         <v/>
       </c>
-      <c r="F24" s="17">
+      <c r="F24" s="19">
         <f>SUM(F16:F23)</f>
         <v/>
       </c>
       <c r="G24" s="13" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -2074,7 +2080,7 @@
       <c r="C25" s="11" t="n"/>
       <c r="D25" s="11" t="n"/>
       <c r="E25" s="12" t="n"/>
-      <c r="F25" s="17">
+      <c r="F25" s="19">
         <f>F24/E24*100</f>
         <v/>
       </c>
@@ -2082,7 +2088,7 @@
     </row>
     <row r="26" ht="9.75" customHeight="1"/>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -2091,11 +2097,11 @@
       <c r="C27" s="11" t="n"/>
       <c r="D27" s="11" t="n"/>
       <c r="E27" s="12" t="n"/>
-      <c r="F27" s="17">
+      <c r="F27" s="19">
         <f>F25*30/100</f>
         <v/>
       </c>
-      <c r="G27" s="17" t="inlineStr">
+      <c r="G27" s="19" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -2270,7 +2276,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="16" t="n">
+      <c r="A16" s="18" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -2294,7 +2300,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="16" t="n">
+      <c r="A17" s="18" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -2318,7 +2324,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="16" t="n">
+      <c r="A18" s="18" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -2342,7 +2348,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="16" t="n">
+      <c r="A19" s="18" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -2366,7 +2372,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="16" t="n">
+      <c r="A20" s="18" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -2390,7 +2396,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="16" t="n">
+      <c r="A21" s="18" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -2414,7 +2420,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="16" t="n">
+      <c r="A22" s="18" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -2438,7 +2444,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="16" t="n">
+      <c r="A23" s="18" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -2462,7 +2468,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="16" t="n">
+      <c r="A24" s="18" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -2486,7 +2492,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="16" t="n">
+      <c r="A25" s="18" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -2510,7 +2516,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="16" t="n">
+      <c r="A26" s="18" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -2534,7 +2540,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="16" t="n">
+      <c r="A27" s="18" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -2558,7 +2564,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="16" t="n">
+      <c r="A28" s="18" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -2582,7 +2588,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="16" t="n">
+      <c r="A29" s="18" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -2606,7 +2612,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="16" t="n">
+      <c r="A30" s="18" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -2630,7 +2636,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="16" t="n">
+      <c r="A31" s="18" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -2654,7 +2660,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="16" t="n">
+      <c r="A32" s="18" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -2678,7 +2684,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="16" t="n">
+      <c r="A33" s="18" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -2702,7 +2708,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="16" t="n">
+      <c r="A34" s="18" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -2726,7 +2732,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -2734,18 +2740,18 @@
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="12" t="n"/>
-      <c r="E35" s="17">
+      <c r="E35" s="19">
         <f>SUM(E16:E34)</f>
         <v/>
       </c>
-      <c r="F35" s="17">
+      <c r="F35" s="19">
         <f>SUM(F16:F34)</f>
         <v/>
       </c>
       <c r="G35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -2754,7 +2760,7 @@
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="12" t="n"/>
-      <c r="F36" s="17">
+      <c r="F36" s="19">
         <f>F35/E35*100</f>
         <v/>
       </c>
@@ -2762,7 +2768,7 @@
     </row>
     <row r="37" ht="9.75" customHeight="1"/>
     <row r="38">
-      <c r="A38" s="17" t="inlineStr">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -2771,11 +2777,11 @@
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="12" t="n"/>
-      <c r="F38" s="17">
+      <c r="F38" s="19">
         <f>F36*30/100</f>
         <v/>
       </c>
-      <c r="G38" s="17" t="inlineStr">
+      <c r="G38" s="19" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -2861,6 +2867,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -2874,6 +2884,10 @@
 Workshop/ lab – 800 sft. (75 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3823,7 +3837,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="16" t="n">
+      <c r="A16" s="18" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -3847,7 +3861,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="16" t="n">
+      <c r="A17" s="18" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -3871,7 +3885,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="16" t="n">
+      <c r="A18" s="18" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -3895,7 +3909,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="16" t="n">
+      <c r="A19" s="18" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -3919,7 +3933,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="16" t="n">
+      <c r="A20" s="18" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -3943,7 +3957,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="16" t="n">
+      <c r="A21" s="18" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -3967,7 +3981,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="16" t="n">
+      <c r="A22" s="18" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -3991,7 +4005,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="16" t="n">
+      <c r="A23" s="18" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -4015,7 +4029,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="16" t="n">
+      <c r="A24" s="18" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -4039,7 +4053,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="16" t="n">
+      <c r="A25" s="18" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -4063,7 +4077,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="16" t="n">
+      <c r="A26" s="18" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -4087,7 +4101,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="16" t="n">
+      <c r="A27" s="18" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -4111,7 +4125,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="16" t="n">
+      <c r="A28" s="18" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -4135,7 +4149,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="16" t="n">
+      <c r="A29" s="18" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -4159,7 +4173,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="16" t="n">
+      <c r="A30" s="18" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -4183,7 +4197,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="16" t="n">
+      <c r="A31" s="18" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -4207,7 +4221,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="16" t="n">
+      <c r="A32" s="18" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -4231,7 +4245,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="16" t="n">
+      <c r="A33" s="18" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -4255,7 +4269,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="16" t="n">
+      <c r="A34" s="18" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -4279,7 +4293,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -4287,18 +4301,18 @@
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="12" t="n"/>
-      <c r="E35" s="17">
+      <c r="E35" s="19">
         <f>SUM(E16:E34)</f>
         <v/>
       </c>
-      <c r="F35" s="17">
+      <c r="F35" s="19">
         <f>SUM(F16:F34)</f>
         <v/>
       </c>
       <c r="G35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -4307,7 +4321,7 @@
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="12" t="n"/>
-      <c r="F36" s="17">
+      <c r="F36" s="19">
         <f>F35/E35*100</f>
         <v/>
       </c>
@@ -4315,7 +4329,7 @@
     </row>
     <row r="37" ht="9.75" customHeight="1"/>
     <row r="38">
-      <c r="A38" s="17" t="inlineStr">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -4324,11 +4338,11 @@
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="12" t="n"/>
-      <c r="F38" s="17">
+      <c r="F38" s="19">
         <f>F36*30/100</f>
         <v/>
       </c>
-      <c r="G38" s="17" t="inlineStr">
+      <c r="G38" s="19" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -4374,6 +4388,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -4396,6 +4411,7 @@
         <v>25</v>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -4438,6 +4454,8 @@
       <c r="F8" s="11" t="n"/>
       <c r="G8" s="12" t="n"/>
     </row>
+    <row r="9"/>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
@@ -4445,6 +4463,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="115.65" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -4456,6 +4475,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="26.85" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
@@ -4495,7 +4515,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="16" t="n">
+      <c r="A16" s="18" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -4519,7 +4539,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="16" t="n">
+      <c r="A17" s="18" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -4543,7 +4563,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="16" t="n">
+      <c r="A18" s="18" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -4567,13 +4587,13 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="16" t="n">
+      <c r="A19" s="18" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Computers/Laptop: 
-(Minimum Intel Core i5 processor (8th Gen), 8GB RAM (16GB preferred), 500GB SSD storage (1TB preferred), High-resolution monitors (19/20-inch minimum, with color accuracy).</t>
+(Minimum Intel core i5 or Intel core i3 6 gen/above, or AMD similar spec, 8GB RAM (16GB preferred), 500GB SSD storage (1TB preferred), High-resolution monitors (19/20-inch minimum, with color accuracy).</t>
         </is>
       </c>
       <c r="C19" s="9" t="n">
@@ -4592,7 +4612,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="16" t="n">
+      <c r="A20" s="18" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -4617,7 +4637,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="16" t="n">
+      <c r="A21" s="18" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -4642,7 +4662,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="16" t="n">
+      <c r="A22" s="18" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -4666,7 +4686,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="16" t="n">
+      <c r="A23" s="18" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -4690,7 +4710,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -4698,18 +4718,18 @@
       <c r="B24" s="11" t="n"/>
       <c r="C24" s="11" t="n"/>
       <c r="D24" s="12" t="n"/>
-      <c r="E24" s="17">
+      <c r="E24" s="19">
         <f>SUM(E16:E23)</f>
         <v/>
       </c>
-      <c r="F24" s="17">
+      <c r="F24" s="19">
         <f>SUM(F16:F23)</f>
         <v/>
       </c>
       <c r="G24" s="13" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -4718,7 +4738,7 @@
       <c r="C25" s="11" t="n"/>
       <c r="D25" s="11" t="n"/>
       <c r="E25" s="12" t="n"/>
-      <c r="F25" s="17">
+      <c r="F25" s="19">
         <f>F24/E24*100</f>
         <v/>
       </c>
@@ -4726,7 +4746,7 @@
     </row>
     <row r="26" ht="9.75" customHeight="1"/>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -4735,11 +4755,11 @@
       <c r="C27" s="11" t="n"/>
       <c r="D27" s="11" t="n"/>
       <c r="E27" s="12" t="n"/>
-      <c r="F27" s="17">
+      <c r="F27" s="19">
         <f>F25*30/100</f>
         <v/>
       </c>
-      <c r="G27" s="17" t="inlineStr">
+      <c r="G27" s="19" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -4913,7 +4933,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="16" t="n">
+      <c r="A16" s="18" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -4937,7 +4957,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="16" t="n">
+      <c r="A17" s="18" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -4961,7 +4981,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="16" t="n">
+      <c r="A18" s="18" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -4985,7 +5005,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="16" t="n">
+      <c r="A19" s="18" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -5009,7 +5029,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="16" t="n">
+      <c r="A20" s="18" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -5033,7 +5053,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="16" t="n">
+      <c r="A21" s="18" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -5057,7 +5077,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="16" t="n">
+      <c r="A22" s="18" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -5081,7 +5101,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="16" t="n">
+      <c r="A23" s="18" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -5105,7 +5125,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="16" t="n">
+      <c r="A24" s="18" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -5129,7 +5149,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="16" t="n">
+      <c r="A25" s="18" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -5153,7 +5173,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="16" t="n">
+      <c r="A26" s="18" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -5177,7 +5197,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="16" t="n">
+      <c r="A27" s="18" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -5201,7 +5221,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="16" t="n">
+      <c r="A28" s="18" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -5225,7 +5245,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="16" t="n">
+      <c r="A29" s="18" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -5249,7 +5269,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="16" t="n">
+      <c r="A30" s="18" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -5273,7 +5293,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="16" t="n">
+      <c r="A31" s="18" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -5297,7 +5317,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="16" t="n">
+      <c r="A32" s="18" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -5321,7 +5341,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="16" t="n">
+      <c r="A33" s="18" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -5345,7 +5365,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="16" t="n">
+      <c r="A34" s="18" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -5369,7 +5389,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35" ht="14.15" customHeight="1">
-      <c r="A35" s="16" t="n">
+      <c r="A35" s="18" t="n">
         <v>20</v>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -5393,7 +5413,7 @@
       <c r="G35" s="9" t="n"/>
     </row>
     <row r="36" ht="14.15" customHeight="1">
-      <c r="A36" s="16" t="n">
+      <c r="A36" s="18" t="n">
         <v>21</v>
       </c>
       <c r="B36" s="8" t="inlineStr">
@@ -5417,7 +5437,7 @@
       <c r="G36" s="9" t="n"/>
     </row>
     <row r="37" ht="14.15" customHeight="1">
-      <c r="A37" s="16" t="n">
+      <c r="A37" s="18" t="n">
         <v>22</v>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -5441,7 +5461,7 @@
       <c r="G37" s="9" t="n"/>
     </row>
     <row r="38" ht="14.15" customHeight="1">
-      <c r="A38" s="16" t="n">
+      <c r="A38" s="18" t="n">
         <v>23</v>
       </c>
       <c r="B38" s="8" t="inlineStr">
@@ -5465,7 +5485,7 @@
       <c r="G38" s="9" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="17" t="inlineStr">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -5473,18 +5493,18 @@
       <c r="B39" s="11" t="n"/>
       <c r="C39" s="11" t="n"/>
       <c r="D39" s="12" t="n"/>
-      <c r="E39" s="17">
+      <c r="E39" s="19">
         <f>SUM(E16:E38)</f>
         <v/>
       </c>
-      <c r="F39" s="17">
+      <c r="F39" s="19">
         <f>SUM(F16:F38)</f>
         <v/>
       </c>
       <c r="G39" s="13" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="17" t="inlineStr">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -5493,7 +5513,7 @@
       <c r="C40" s="11" t="n"/>
       <c r="D40" s="11" t="n"/>
       <c r="E40" s="12" t="n"/>
-      <c r="F40" s="17">
+      <c r="F40" s="19">
         <f>F39/E39*100</f>
         <v/>
       </c>
@@ -5501,7 +5521,7 @@
     </row>
     <row r="41" ht="9.75" customHeight="1"/>
     <row r="42">
-      <c r="A42" s="17" t="inlineStr">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -5510,11 +5530,11 @@
       <c r="C42" s="11" t="n"/>
       <c r="D42" s="11" t="n"/>
       <c r="E42" s="12" t="n"/>
-      <c r="F42" s="17">
+      <c r="F42" s="19">
         <f>F40*30/100</f>
         <v/>
       </c>
-      <c r="G42" s="17" t="inlineStr">
+      <c r="G42" s="19" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -5680,7 +5700,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="16" t="n">
+      <c r="A16" s="18" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -5704,7 +5724,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="16" t="n">
+      <c r="A17" s="18" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -5728,7 +5748,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="16" t="n">
+      <c r="A18" s="18" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -5752,7 +5772,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="16" t="n">
+      <c r="A19" s="18" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -5776,7 +5796,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="16" t="n">
+      <c r="A20" s="18" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -5800,7 +5820,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="16" t="n">
+      <c r="A21" s="18" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -5824,7 +5844,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="16" t="n">
+      <c r="A22" s="18" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -5848,7 +5868,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="16" t="n">
+      <c r="A23" s="18" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -5872,7 +5892,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="16" t="n">
+      <c r="A24" s="18" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -5896,7 +5916,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="16" t="n">
+      <c r="A25" s="18" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -5920,7 +5940,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="16" t="n">
+      <c r="A26" s="18" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -5944,7 +5964,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="16" t="n">
+      <c r="A27" s="18" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -5968,7 +5988,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="16" t="n">
+      <c r="A28" s="18" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -5992,7 +6012,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="16" t="n">
+      <c r="A29" s="18" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -6016,7 +6036,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="16" t="n">
+      <c r="A30" s="18" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -6040,7 +6060,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="16" t="n">
+      <c r="A31" s="18" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -6064,7 +6084,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="16" t="n">
+      <c r="A32" s="18" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -6088,7 +6108,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="16" t="n">
+      <c r="A33" s="18" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -6112,7 +6132,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -6120,18 +6140,18 @@
       <c r="B34" s="11" t="n"/>
       <c r="C34" s="11" t="n"/>
       <c r="D34" s="12" t="n"/>
-      <c r="E34" s="17">
+      <c r="E34" s="19">
         <f>SUM(E16:E33)</f>
         <v/>
       </c>
-      <c r="F34" s="17">
+      <c r="F34" s="19">
         <f>SUM(F16:F33)</f>
         <v/>
       </c>
       <c r="G34" s="13" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -6140,7 +6160,7 @@
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="11" t="n"/>
       <c r="E35" s="12" t="n"/>
-      <c r="F35" s="17">
+      <c r="F35" s="19">
         <f>F34/E34*100</f>
         <v/>
       </c>
@@ -6148,7 +6168,7 @@
     </row>
     <row r="36" ht="9.75" customHeight="1"/>
     <row r="37">
-      <c r="A37" s="17" t="inlineStr">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -6157,11 +6177,11 @@
       <c r="C37" s="11" t="n"/>
       <c r="D37" s="11" t="n"/>
       <c r="E37" s="12" t="n"/>
-      <c r="F37" s="17">
+      <c r="F37" s="19">
         <f>F35*30/100</f>
         <v/>
       </c>
-      <c r="G37" s="17" t="inlineStr">
+      <c r="G37" s="19" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -6327,7 +6347,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="16" t="n">
+      <c r="A16" s="18" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -6351,7 +6371,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="16" t="n">
+      <c r="A17" s="18" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -6375,7 +6395,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="16" t="n">
+      <c r="A18" s="18" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -6399,7 +6419,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="16" t="n">
+      <c r="A19" s="18" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -6423,7 +6443,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="16" t="n">
+      <c r="A20" s="18" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -6447,7 +6467,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="16" t="n">
+      <c r="A21" s="18" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -6471,7 +6491,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="16" t="n">
+      <c r="A22" s="18" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -6495,7 +6515,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="16" t="n">
+      <c r="A23" s="18" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -6519,7 +6539,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="16" t="n">
+      <c r="A24" s="18" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -6543,7 +6563,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="16" t="n">
+      <c r="A25" s="18" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -6567,7 +6587,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="16" t="n">
+      <c r="A26" s="18" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -6591,7 +6611,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="16" t="n">
+      <c r="A27" s="18" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -6615,7 +6635,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="16" t="n">
+      <c r="A28" s="18" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -6639,7 +6659,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="16" t="n">
+      <c r="A29" s="18" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -6663,7 +6683,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="16" t="n">
+      <c r="A30" s="18" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -6687,7 +6707,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="16" t="n">
+      <c r="A31" s="18" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -6711,7 +6731,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="16" t="n">
+      <c r="A32" s="18" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -6735,7 +6755,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="16" t="n">
+      <c r="A33" s="18" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -6759,7 +6779,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="16" t="n">
+      <c r="A34" s="18" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -6783,7 +6803,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35" ht="14.15" customHeight="1">
-      <c r="A35" s="16" t="n">
+      <c r="A35" s="18" t="n">
         <v>20</v>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -6807,7 +6827,7 @@
       <c r="G35" s="9" t="n"/>
     </row>
     <row r="36" ht="14.15" customHeight="1">
-      <c r="A36" s="16" t="n">
+      <c r="A36" s="18" t="n">
         <v>21</v>
       </c>
       <c r="B36" s="8" t="inlineStr">
@@ -6831,7 +6851,7 @@
       <c r="G36" s="9" t="n"/>
     </row>
     <row r="37" ht="14.15" customHeight="1">
-      <c r="A37" s="16" t="n">
+      <c r="A37" s="18" t="n">
         <v>22</v>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -6855,7 +6875,7 @@
       <c r="G37" s="9" t="n"/>
     </row>
     <row r="38" ht="14.15" customHeight="1">
-      <c r="A38" s="16" t="n">
+      <c r="A38" s="18" t="n">
         <v>23</v>
       </c>
       <c r="B38" s="8" t="inlineStr">
@@ -6879,7 +6899,7 @@
       <c r="G38" s="9" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="17" t="inlineStr">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -6887,18 +6907,18 @@
       <c r="B39" s="11" t="n"/>
       <c r="C39" s="11" t="n"/>
       <c r="D39" s="12" t="n"/>
-      <c r="E39" s="17">
+      <c r="E39" s="19">
         <f>SUM(E16:E38)</f>
         <v/>
       </c>
-      <c r="F39" s="17">
+      <c r="F39" s="19">
         <f>SUM(F16:F38)</f>
         <v/>
       </c>
       <c r="G39" s="13" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="17" t="inlineStr">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -6907,7 +6927,7 @@
       <c r="C40" s="11" t="n"/>
       <c r="D40" s="11" t="n"/>
       <c r="E40" s="12" t="n"/>
-      <c r="F40" s="17">
+      <c r="F40" s="19">
         <f>F39/E39*100</f>
         <v/>
       </c>
@@ -6915,7 +6935,7 @@
     </row>
     <row r="41" ht="9.75" customHeight="1"/>
     <row r="42">
-      <c r="A42" s="17" t="inlineStr">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -6924,11 +6944,11 @@
       <c r="C42" s="11" t="n"/>
       <c r="D42" s="11" t="n"/>
       <c r="E42" s="12" t="n"/>
-      <c r="F42" s="17">
+      <c r="F42" s="19">
         <f>F40*30/100</f>
         <v/>
       </c>
-      <c r="G42" s="17" t="inlineStr">
+      <c r="G42" s="19" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -7095,7 +7115,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="16" t="n">
+      <c r="A16" s="18" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -7119,7 +7139,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="16" t="n">
+      <c r="A17" s="18" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -7143,7 +7163,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="16" t="n">
+      <c r="A18" s="18" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -7167,7 +7187,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="16" t="n">
+      <c r="A19" s="18" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -7191,7 +7211,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="16" t="n">
+      <c r="A20" s="18" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -7215,7 +7235,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="16" t="n">
+      <c r="A21" s="18" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -7239,7 +7259,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="16" t="n">
+      <c r="A22" s="18" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -7263,7 +7283,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="16" t="n">
+      <c r="A23" s="18" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -7287,7 +7307,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="16" t="n">
+      <c r="A24" s="18" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -7311,7 +7331,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="16" t="n">
+      <c r="A25" s="18" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -7335,7 +7355,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="16" t="n">
+      <c r="A26" s="18" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -7359,7 +7379,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="16" t="n">
+      <c r="A27" s="18" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -7383,7 +7403,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="16" t="n">
+      <c r="A28" s="18" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -7407,7 +7427,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="16" t="n">
+      <c r="A29" s="18" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -7431,7 +7451,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="16" t="n">
+      <c r="A30" s="18" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -7455,7 +7475,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="16" t="n">
+      <c r="A31" s="18" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -7479,7 +7499,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="16" t="n">
+      <c r="A32" s="18" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -7503,7 +7523,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="16" t="n">
+      <c r="A33" s="18" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -7527,7 +7547,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="16" t="n">
+      <c r="A34" s="18" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -7551,7 +7571,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35" ht="14.15" customHeight="1">
-      <c r="A35" s="16" t="n">
+      <c r="A35" s="18" t="n">
         <v>20</v>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -7575,7 +7595,7 @@
       <c r="G35" s="9" t="n"/>
     </row>
     <row r="36" ht="14.15" customHeight="1">
-      <c r="A36" s="16" t="n">
+      <c r="A36" s="18" t="n">
         <v>21</v>
       </c>
       <c r="B36" s="8" t="inlineStr">
@@ -7599,7 +7619,7 @@
       <c r="G36" s="9" t="n"/>
     </row>
     <row r="37" ht="14.15" customHeight="1">
-      <c r="A37" s="16" t="n">
+      <c r="A37" s="18" t="n">
         <v>22</v>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -7623,7 +7643,7 @@
       <c r="G37" s="9" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="17" t="inlineStr">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -7631,18 +7651,18 @@
       <c r="B38" s="11" t="n"/>
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="12" t="n"/>
-      <c r="E38" s="17">
+      <c r="E38" s="19">
         <f>SUM(E16:E37)</f>
         <v/>
       </c>
-      <c r="F38" s="17">
+      <c r="F38" s="19">
         <f>SUM(F16:F37)</f>
         <v/>
       </c>
       <c r="G38" s="13" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="17" t="inlineStr">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -7651,7 +7671,7 @@
       <c r="C39" s="11" t="n"/>
       <c r="D39" s="11" t="n"/>
       <c r="E39" s="12" t="n"/>
-      <c r="F39" s="17">
+      <c r="F39" s="19">
         <f>F38/E38*100</f>
         <v/>
       </c>
@@ -7659,7 +7679,7 @@
     </row>
     <row r="40" ht="9.75" customHeight="1"/>
     <row r="41">
-      <c r="A41" s="17" t="inlineStr">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -7668,11 +7688,11 @@
       <c r="C41" s="11" t="n"/>
       <c r="D41" s="11" t="n"/>
       <c r="E41" s="12" t="n"/>
-      <c r="F41" s="17">
+      <c r="F41" s="19">
         <f>F39*30/100</f>
         <v/>
       </c>
-      <c r="G41" s="17" t="inlineStr">
+      <c r="G41" s="19" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -7838,7 +7858,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="16" t="n">
+      <c r="A16" s="18" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -7862,7 +7882,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="16" t="n">
+      <c r="A17" s="18" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -7886,7 +7906,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="16" t="n">
+      <c r="A18" s="18" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -7910,7 +7930,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="16" t="n">
+      <c r="A19" s="18" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -7934,7 +7954,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="16" t="n">
+      <c r="A20" s="18" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -7958,7 +7978,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="16" t="n">
+      <c r="A21" s="18" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -7982,7 +8002,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="16" t="n">
+      <c r="A22" s="18" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -8006,7 +8026,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="16" t="n">
+      <c r="A23" s="18" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -8030,7 +8050,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="16" t="n">
+      <c r="A24" s="18" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -8054,7 +8074,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="16" t="n">
+      <c r="A25" s="18" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -8078,7 +8098,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="16" t="n">
+      <c r="A26" s="18" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -8102,7 +8122,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="16" t="n">
+      <c r="A27" s="18" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -8126,7 +8146,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="16" t="n">
+      <c r="A28" s="18" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -8150,7 +8170,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="16" t="n">
+      <c r="A29" s="18" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -8174,7 +8194,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="16" t="n">
+      <c r="A30" s="18" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -8198,7 +8218,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="16" t="n">
+      <c r="A31" s="18" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -8222,7 +8242,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="16" t="n">
+      <c r="A32" s="18" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -8246,7 +8266,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="16" t="n">
+      <c r="A33" s="18" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -8270,7 +8290,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="16" t="n">
+      <c r="A34" s="18" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -8294,7 +8314,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35" ht="14.15" customHeight="1">
-      <c r="A35" s="16" t="n">
+      <c r="A35" s="18" t="n">
         <v>20</v>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -8318,7 +8338,7 @@
       <c r="G35" s="9" t="n"/>
     </row>
     <row r="36" ht="14.15" customHeight="1">
-      <c r="A36" s="16" t="n">
+      <c r="A36" s="18" t="n">
         <v>21</v>
       </c>
       <c r="B36" s="8" t="inlineStr">
@@ -8342,7 +8362,7 @@
       <c r="G36" s="9" t="n"/>
     </row>
     <row r="37" ht="14.15" customHeight="1">
-      <c r="A37" s="16" t="n">
+      <c r="A37" s="18" t="n">
         <v>22</v>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -8366,7 +8386,7 @@
       <c r="G37" s="9" t="n"/>
     </row>
     <row r="38" ht="14.15" customHeight="1">
-      <c r="A38" s="16" t="n">
+      <c r="A38" s="18" t="n">
         <v>23</v>
       </c>
       <c r="B38" s="8" t="inlineStr">
@@ -8390,7 +8410,7 @@
       <c r="G38" s="9" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="17" t="inlineStr">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -8398,18 +8418,18 @@
       <c r="B39" s="11" t="n"/>
       <c r="C39" s="11" t="n"/>
       <c r="D39" s="12" t="n"/>
-      <c r="E39" s="17">
+      <c r="E39" s="19">
         <f>SUM(E16:E38)</f>
         <v/>
       </c>
-      <c r="F39" s="17">
+      <c r="F39" s="19">
         <f>SUM(F16:F38)</f>
         <v/>
       </c>
       <c r="G39" s="13" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="17" t="inlineStr">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -8418,7 +8438,7 @@
       <c r="C40" s="11" t="n"/>
       <c r="D40" s="11" t="n"/>
       <c r="E40" s="12" t="n"/>
-      <c r="F40" s="17">
+      <c r="F40" s="19">
         <f>F39/E39*100</f>
         <v/>
       </c>
@@ -8426,7 +8446,7 @@
     </row>
     <row r="41" ht="9.75" customHeight="1"/>
     <row r="42">
-      <c r="A42" s="17" t="inlineStr">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -8435,11 +8455,11 @@
       <c r="C42" s="11" t="n"/>
       <c r="D42" s="11" t="n"/>
       <c r="E42" s="12" t="n"/>
-      <c r="F42" s="17">
+      <c r="F42" s="19">
         <f>F40*30/100</f>
         <v/>
       </c>
-      <c r="G42" s="17" t="inlineStr">
+      <c r="G42" s="19" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -8604,7 +8624,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="16" t="n">
+      <c r="A16" s="18" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -8628,7 +8648,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="16" t="n">
+      <c r="A17" s="18" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -8652,7 +8672,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="16" t="n">
+      <c r="A18" s="18" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -8676,7 +8696,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="16" t="n">
+      <c r="A19" s="18" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -8700,7 +8720,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="16" t="n">
+      <c r="A20" s="18" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -8724,7 +8744,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="16" t="n">
+      <c r="A21" s="18" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -8748,7 +8768,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="16" t="n">
+      <c r="A22" s="18" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -8772,7 +8792,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="16" t="n">
+      <c r="A23" s="18" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -8796,7 +8816,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="16" t="n">
+      <c r="A24" s="18" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -8820,7 +8840,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="16" t="n">
+      <c r="A25" s="18" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -8844,7 +8864,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="16" t="n">
+      <c r="A26" s="18" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -8868,7 +8888,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="16" t="n">
+      <c r="A27" s="18" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -8892,7 +8912,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="16" t="n">
+      <c r="A28" s="18" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -8916,7 +8936,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="16" t="n">
+      <c r="A29" s="18" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -8940,7 +8960,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="16" t="n">
+      <c r="A30" s="18" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -8964,7 +8984,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="16" t="n">
+      <c r="A31" s="18" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -8988,7 +9008,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="16" t="n">
+      <c r="A32" s="18" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -9012,7 +9032,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="16" t="n">
+      <c r="A33" s="18" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -9036,7 +9056,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -9044,18 +9064,18 @@
       <c r="B34" s="11" t="n"/>
       <c r="C34" s="11" t="n"/>
       <c r="D34" s="12" t="n"/>
-      <c r="E34" s="17">
+      <c r="E34" s="19">
         <f>SUM(E16:E33)</f>
         <v/>
       </c>
-      <c r="F34" s="17">
+      <c r="F34" s="19">
         <f>SUM(F16:F33)</f>
         <v/>
       </c>
       <c r="G34" s="13" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -9064,7 +9084,7 @@
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="11" t="n"/>
       <c r="E35" s="12" t="n"/>
-      <c r="F35" s="17">
+      <c r="F35" s="19">
         <f>F34/E34*100</f>
         <v/>
       </c>
@@ -9072,7 +9092,7 @@
     </row>
     <row r="36" ht="9.75" customHeight="1"/>
     <row r="37">
-      <c r="A37" s="17" t="inlineStr">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -9081,11 +9101,11 @@
       <c r="C37" s="11" t="n"/>
       <c r="D37" s="11" t="n"/>
       <c r="E37" s="12" t="n"/>
-      <c r="F37" s="17">
+      <c r="F37" s="19">
         <f>F35*30/100</f>
         <v/>
       </c>
-      <c r="G37" s="17" t="inlineStr">
+      <c r="G37" s="19" t="inlineStr">
         <is>
           <t>Points</t>
         </is>

--- a/lab-standards/PKSF-lab-standard.xlsx
+++ b/lab-standards/PKSF-lab-standard.xlsx
@@ -1313,6 +1313,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1335,6 +1336,7 @@
         <v>25</v>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -1377,6 +1379,8 @@
       <c r="F8" s="11" t="n"/>
       <c r="G8" s="12" t="n"/>
     </row>
+    <row r="9"/>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
@@ -1384,6 +1388,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="115.65" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -1395,6 +1400,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="26.85" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
@@ -1439,7 +1445,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Laptop/ Desktop (Minimum Intel core i5 or Intel core i3 6 gen/above, or AMD Ryzen 5/ similar spec; Ram: minimum 8 - 16 GB; Display: FHD monitor; Graphic Card: dedicated GPU 2GB; High Speed Internet (Minimum 10 Mbps); Graphic Design Software 
+          <t>Laptop/ Desktop (Minimum Intel core i5 or Intel core i3 8 gen/above, or AMD Ryzen 5/ similar spec; Ram: minimum 8 - 16 GB; Display: FHD monitor; Graphic Card: dedicated GPU 2GB; High Speed Internet (Minimum 10 Mbps); Graphic Design Software 
 (Photoshop CC, Illustrator CC, InDesign, After Effects, CorelDraw); 3D Design Software (Blender, Cinema 4D or Autodesk Maya)</t>
         </is>
       </c>
@@ -1730,7 +1736,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1753,7 +1758,6 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -1796,8 +1800,6 @@
       <c r="F8" s="11" t="n"/>
       <c r="G8" s="12" t="n"/>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
@@ -1805,7 +1807,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13" ht="115.65" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -1817,7 +1818,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="26.85" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
@@ -4388,7 +4388,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -4411,7 +4410,6 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -4454,8 +4452,6 @@
       <c r="F8" s="11" t="n"/>
       <c r="G8" s="12" t="n"/>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
@@ -4463,7 +4459,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13" ht="115.65" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -4475,7 +4470,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="26.85" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>

--- a/lab-standards/PKSF-lab-standard.xlsx
+++ b/lab-standards/PKSF-lab-standard.xlsx
@@ -1445,7 +1445,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Laptop/ Desktop (Minimum Intel core i5 or Intel core i3 8 gen/above, or AMD Ryzen 5/ similar spec; Ram: minimum 8 - 16 GB; Display: FHD monitor; Graphic Card: dedicated GPU 2GB; High Speed Internet (Minimum 10 Mbps); Graphic Design Software 
+          <t>Laptop/ Desktop (Minimum Intel core i5 or Intel core i3 8 gen/above, or AMD Ryzen similar spec; Ram: minimum 8 - 16 GB; Display: FHD monitor; Graphic Card: dedicated GPU 2GB; High Speed Internet (Minimum 10 Mbps); Graphic Design Software 
 (Photoshop CC, Illustrator CC, InDesign, After Effects, CorelDraw); 3D Design Software (Blender, Cinema 4D or Autodesk Maya)</t>
         </is>
       </c>
@@ -1736,6 +1736,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1758,6 +1759,7 @@
         <v>25</v>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -1800,6 +1802,8 @@
       <c r="F8" s="11" t="n"/>
       <c r="G8" s="12" t="n"/>
     </row>
+    <row r="9"/>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
@@ -1807,6 +1811,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="115.65" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -1818,6 +1823,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="26.85" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
@@ -1935,7 +1941,7 @@
       <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Computers/Laptop: 
-(Minimum Intel core i5 or Intel core i3 6 gen/above, or AMD similar spec, 8GB RAM (16GB preferred), 500GB SSD storage (1TB preferred), High-resolution monitors (19/20-inch minimum, with color accuracy).</t>
+(Minimum Intel core i5 or Intel core i3 6 gen/above, or AMD Ryzen similar spec, 8GB RAM (16GB preferred), 500GB SSD storage (1TB preferred), High-resolution monitors (19/20-inch minimum, with color accuracy).</t>
         </is>
       </c>
       <c r="C19" s="9" t="n">
@@ -4388,6 +4394,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -4410,6 +4417,7 @@
         <v>25</v>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -4452,6 +4460,8 @@
       <c r="F8" s="11" t="n"/>
       <c r="G8" s="12" t="n"/>
     </row>
+    <row r="9"/>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
@@ -4459,6 +4469,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="115.65" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -4470,6 +4481,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="26.85" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
@@ -4587,7 +4599,7 @@
       <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Computers/Laptop: 
-(Minimum Intel core i5 or Intel core i3 6 gen/above, or AMD similar spec, 8GB RAM (16GB preferred), 500GB SSD storage (1TB preferred), High-resolution monitors (19/20-inch minimum, with color accuracy).</t>
+(Minimum Intel core i5 or Intel core i3 6 gen/above, or AMD Ryzen similar spec, 8GB RAM (16GB preferred), 500GB SSD storage (1TB preferred), High-resolution monitors (19/20-inch minimum, with color accuracy).</t>
         </is>
       </c>
       <c r="C19" s="9" t="n">

--- a/lab-standards/PKSF-lab-standard.xlsx
+++ b/lab-standards/PKSF-lab-standard.xlsx
@@ -1313,7 +1313,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1336,7 +1335,6 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -1379,8 +1377,6 @@
       <c r="F8" s="11" t="n"/>
       <c r="G8" s="12" t="n"/>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
@@ -1388,7 +1384,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13" ht="115.65" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -1400,7 +1395,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="26.85" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
@@ -1736,7 +1730,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1759,7 +1752,6 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -1802,8 +1794,6 @@
       <c r="F8" s="11" t="n"/>
       <c r="G8" s="12" t="n"/>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
@@ -1811,7 +1801,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13" ht="115.65" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -1823,7 +1812,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="26.85" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
@@ -4394,7 +4382,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -4417,7 +4404,6 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -4460,8 +4446,6 @@
       <c r="F8" s="11" t="n"/>
       <c r="G8" s="12" t="n"/>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
@@ -4469,7 +4453,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13" ht="115.65" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -4481,7 +4464,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="26.85" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
@@ -6214,7 +6196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.17" customWidth="1" min="1" max="1"/>
@@ -6960,13 +6942,21 @@
         </is>
       </c>
     </row>
+    <row r="43" ht="28.3" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>* For this course, the institute should have at least 15 channel wiring boards/booths and 3 concealed wiring booths. Otherwise, the total points achieved will be halved.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A42:E42"/>
     <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A43:G43"/>
     <mergeCell ref="A41:G41"/>
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="A40:E40"/>
